--- a/artfynd/A 65569-2019 artfynd.xlsx
+++ b/artfynd/A 65569-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -918,6 +918,117 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>95647934</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91300</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>789</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Raggtaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum mirabile</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Morsfarsmyran, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>571527</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7145046</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-08-22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-08-22</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 65569-2019 artfynd.xlsx
+++ b/artfynd/A 65569-2019 artfynd.xlsx
@@ -928,7 +928,7 @@
         <v>95647934</v>
       </c>
       <c r="B4" t="n">
-        <v>91300</v>
+        <v>91316</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 65569-2019 artfynd.xlsx
+++ b/artfynd/A 65569-2019 artfynd.xlsx
@@ -928,7 +928,7 @@
         <v>95647934</v>
       </c>
       <c r="B4" t="n">
-        <v>91316</v>
+        <v>91328</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 65569-2019 artfynd.xlsx
+++ b/artfynd/A 65569-2019 artfynd.xlsx
@@ -928,7 +928,7 @@
         <v>95647934</v>
       </c>
       <c r="B4" t="n">
-        <v>91328</v>
+        <v>91350</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 65569-2019 artfynd.xlsx
+++ b/artfynd/A 65569-2019 artfynd.xlsx
@@ -928,7 +928,7 @@
         <v>95647934</v>
       </c>
       <c r="B4" t="n">
-        <v>91350</v>
+        <v>91354</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 65569-2019 artfynd.xlsx
+++ b/artfynd/A 65569-2019 artfynd.xlsx
@@ -928,7 +928,7 @@
         <v>95647934</v>
       </c>
       <c r="B4" t="n">
-        <v>91354</v>
+        <v>91360</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 65569-2019 artfynd.xlsx
+++ b/artfynd/A 65569-2019 artfynd.xlsx
@@ -928,7 +928,7 @@
         <v>95647934</v>
       </c>
       <c r="B4" t="n">
-        <v>91360</v>
+        <v>91367</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 65569-2019 artfynd.xlsx
+++ b/artfynd/A 65569-2019 artfynd.xlsx
@@ -928,7 +928,7 @@
         <v>95647934</v>
       </c>
       <c r="B4" t="n">
-        <v>91367</v>
+        <v>91372</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 65569-2019 artfynd.xlsx
+++ b/artfynd/A 65569-2019 artfynd.xlsx
@@ -928,7 +928,7 @@
         <v>95647934</v>
       </c>
       <c r="B4" t="n">
-        <v>91372</v>
+        <v>91400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 65569-2019 artfynd.xlsx
+++ b/artfynd/A 65569-2019 artfynd.xlsx
@@ -928,7 +928,7 @@
         <v>95647934</v>
       </c>
       <c r="B4" t="n">
-        <v>91400</v>
+        <v>91404</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 65569-2019 artfynd.xlsx
+++ b/artfynd/A 65569-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
